--- a/www/download/IND.empe.s.un.EXI382.xlsx
+++ b/www/download/IND.empe.s.un.EXI382.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Number of employee</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,144 +688,144 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9.298</t>
+          <t>9298208.21915253</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.498</t>
+          <t>6498499.99999991</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7.063</t>
+          <t>7062599.99999862</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7119700.00000065</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>7319700.00000304</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7.456</t>
+          <t>7455799.99999858</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7.688</t>
+          <t>7687800.00000113</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>7.833</t>
+          <t>7832699.99999792</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>7.964</t>
+          <t>7964499.99999884</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>8.196</t>
+          <t>8195500.00000254</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>8.355</t>
+          <t>8354599.99999786</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>8.678</t>
+          <t>8678100.00000006</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>8.944</t>
+          <t>8943500.00000008</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>9.252</t>
+          <t>9251899.99999874</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>9.472</t>
+          <t>9472000.00000179</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.629</t>
+          <t>9628799.99999999</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>9.889</t>
+          <t>9889400.00000153</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>10.072</t>
+          <t>10072300.0000012</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>10.213</t>
+          <t>10213199.9999989</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>9.209</t>
+          <t>9208729.17218387</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>8.502</t>
+          <t>8502097.35789649</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>8.655</t>
+          <t>8655096.26435334</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>8770455.79968284</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.037</t>
+          <t>9037083.34929747</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>8.621</t>
+          <t>8621242.53227029</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>8.468</t>
+          <t>8467581.1606716</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>8.483</t>
+          <t>8482628.89335786</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -830,144 +835,144 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.174</t>
+          <t>4173789.53588187</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.873</t>
+          <t>2873449.99999955</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2.659</t>
+          <t>2658979.99999966</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3.041</t>
+          <t>3041189.99999991</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.145</t>
+          <t>3144610.00000043</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.175</t>
+          <t>3175220.00000145</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.031</t>
+          <t>3030850.00000004</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.081</t>
+          <t>3081080.0000005</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3259600.00000108</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3.095</t>
+          <t>3095229.99999989</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3.292</t>
+          <t>3291589.99999929</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3.329</t>
+          <t>3329259.99999996</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>3.385</t>
+          <t>3385479.99999899</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3.375</t>
+          <t>3374890.00000068</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>3.491</t>
+          <t>3490939.99999942</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>3.497</t>
+          <t>3496580.00000006</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>3.527</t>
+          <t>3527069.99999991</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>3.592</t>
+          <t>3591549.9999994</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>3.617</t>
+          <t>3616609.99999948</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3.609</t>
+          <t>3608578.15021365</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>3.642</t>
+          <t>3642070.24622476</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>3.741</t>
+          <t>3741438.90442356</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>3.878</t>
+          <t>3878386.78251025</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.021</t>
+          <t>4020925.54843851</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4230333.49839507</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>4.236</t>
+          <t>4236294.0364956</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>4.231</t>
+          <t>4231179.94858693</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -977,144 +982,144 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4079911.00065386</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.092</t>
+          <t>3091999.9999987</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3.096</t>
+          <t>3096400.00000028</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3.204</t>
+          <t>3203799.99999948</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3.189</t>
+          <t>3189100.00000091</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.328</t>
+          <t>3328100.00000075</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.412</t>
+          <t>3411700.00000003</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.475</t>
+          <t>3474600.0000003</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>3.473</t>
+          <t>3472799.99999998</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>3.471</t>
+          <t>3470800.00000147</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>3.509</t>
+          <t>3508699.99999958</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>3.566</t>
+          <t>3565799.99999867</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>3.608</t>
+          <t>3607799.99999881</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>3.673</t>
+          <t>3672799.99999985</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>3.742</t>
+          <t>3742499.99999991</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>3.728</t>
+          <t>3728400.00000058</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>3.752</t>
+          <t>3752300.00000054</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>3.782</t>
+          <t>3781999.99999899</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3810399.99999946</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3.807</t>
+          <t>3806801.58966752</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3.718</t>
+          <t>3717733.85306004</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>3.822</t>
+          <t>3821637.22971967</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>3.881</t>
+          <t>3880896.00805397</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.993</t>
+          <t>3992892.66059232</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>4.049</t>
+          <t>4048714.59421854</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4060035.68049983</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>4.042</t>
+          <t>4041653.42500636</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1124,144 +1129,144 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.343</t>
+          <t>4343177.3856775</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.767</t>
+          <t>2766899.99999952</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.688</t>
+          <t>2687600.00000056</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2.553</t>
+          <t>2553400.00000093</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.414</t>
+          <t>2414100.00000008</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.473</t>
+          <t>2473299.9999994</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.264</t>
+          <t>2264499.99999961</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.378</t>
+          <t>2378400.00000038</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.374</t>
+          <t>2373699.99999925</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2.524</t>
+          <t>2524200.00000073</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2.581</t>
+          <t>2581200.0000003</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2630499.9999991</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2729500.00000031</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.832</t>
+          <t>2831900.00000037</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.936</t>
+          <t>2936499.99999959</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2.806</t>
+          <t>2805700.0000006</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2.655</t>
+          <t>2654800.00000034</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2600099.99999917</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2.587</t>
+          <t>2587399.99999985</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2.471</t>
+          <t>2470984.2192587</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2.635</t>
+          <t>2634524.3396801</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2.784</t>
+          <t>2784163.06515899</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2.879</t>
+          <t>2879207.83751004</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.082</t>
+          <t>3081558.62350159</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3.393</t>
+          <t>3393161.14072728</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>3.673</t>
+          <t>3673091.28853288</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>3.865</t>
+          <t>3865331.08158036</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1271,144 +1276,144 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>56.982</t>
+          <t>56981967.2398076</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>42.363</t>
+          <t>42362699.9999964</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>42.802</t>
+          <t>42802199.9999922</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>42.814</t>
+          <t>42814299.9999988</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>43.065</t>
+          <t>43064700.0000053</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>43.456</t>
+          <t>43455500.0000115</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>45.732</t>
+          <t>45732100.0000117</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>48.182</t>
+          <t>48181500.0000085</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>48.908</t>
+          <t>48908400.0000226</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>49.728</t>
+          <t>49728000.0000001</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>53.127</t>
+          <t>53127499.9999828</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>54.684</t>
+          <t>54684199.9999904</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>56.818</t>
+          <t>56817700.0000132</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>58.749</t>
+          <t>58749499.99997</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>60130200.0000049</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>61.511</t>
+          <t>61511000.0000139</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>62.524</t>
+          <t>62524049.9999867</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>63.538</t>
+          <t>63537799.9999794</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>64.922</t>
+          <t>64921600.0000059</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>62.52</t>
+          <t>62519723.5654522</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>61.764</t>
+          <t>61764009.7988428</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>51.48</t>
+          <t>51480173.3395316</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>51.846</t>
+          <t>51846006.6961075</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>59.099</t>
+          <t>59098718.0697952</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>52.794</t>
+          <t>52794341.342471</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>54.102</t>
+          <t>54102428.5375113</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>51.703</t>
+          <t>51702997.2733888</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1418,144 +1423,144 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>12.472</t>
+          <t>12472067.2594807</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11.717</t>
+          <t>11716909.9999972</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10.609</t>
+          <t>10608720.0000029</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>11.227</t>
+          <t>11226509.9999999</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>11.452</t>
+          <t>11451894.9999991</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>13.03</t>
+          <t>13030424.9999991</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>13.466</t>
+          <t>13466439.9999994</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13.649</t>
+          <t>13649409.999998</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>14.043</t>
+          <t>14043385.000002</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>14.353</t>
+          <t>14352939.9999959</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>14640495.0000001</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>13.48</t>
+          <t>13480170.0000008</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>15.155</t>
+          <t>15154650.0000004</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>15.468</t>
+          <t>15468040.0000034</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>15.765</t>
+          <t>15765015.0000006</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>14.251</t>
+          <t>14251219.9999969</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>15.751</t>
+          <t>15750544.9999981</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>16059525.0000018</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>16.248</t>
+          <t>16247640.0000012</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>15.129</t>
+          <t>15128504.8654034</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>14.055</t>
+          <t>14054878.3985563</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>13.974</t>
+          <t>13973586.4417755</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>13.404</t>
+          <t>13403692.6579194</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13.378</t>
+          <t>13377857.3360745</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>12.807</t>
+          <t>12807250.1529469</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13.417</t>
+          <t>13416660.8366175</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>12.994</t>
+          <t>12993767.8215628</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1565,144 +1570,144 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>420.435</t>
+          <t>420435281.218323</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>137.543</t>
+          <t>137543499.99994</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>140.97</t>
+          <t>140969900.000026</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>138.781</t>
+          <t>138780600.000164</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>116.164</t>
+          <t>116163699.999824</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>111.719</t>
+          <t>111718599.999955</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>105.549</t>
+          <t>105549099.999935</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>100.925</t>
+          <t>100924800.000031</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>98.314</t>
+          <t>98313500.0000294</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>98.068</t>
+          <t>98067500.000134</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>98.664</t>
+          <t>98664499.9997911</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>100.987</t>
+          <t>100986900.000078</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>103.689</t>
+          <t>103688899.999605</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>106.082</t>
+          <t>106081800.000074</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>86.274</t>
+          <t>86274400.000185</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>94.359</t>
+          <t>94358700.0000582</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>113.472</t>
+          <t>113471900.000122</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>125.843</t>
+          <t>125843399.999918</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>132.875</t>
+          <t>132875499.99985</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>162.417</t>
+          <t>162417236.287276</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>180.016</t>
+          <t>180016404.613191</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>244.74</t>
+          <t>244739833.778951</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>248.214</t>
+          <t>248214394.671774</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>259.001</t>
+          <t>259001079.975295</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>285.377</t>
+          <t>285376718.067178</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>313.784</t>
+          <t>313783930.774719</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>330.596</t>
+          <t>330596373.56668</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1712,144 +1717,144 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>432702.018267156</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>207099.999999989</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>209149.999999906</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>211400.000000048</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>213250.000000058</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>212600.00000002</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>220699.999999996</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>234000.000000087</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>243200.000000039</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>249199.999999985</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>257899.99999996</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>267800.000000001</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>279599.999999931</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>300499.99999999</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>311799.999999906</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>312700.000000024</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>327000.000000024</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>327600.000000067</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>326099.999999918</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>302398.9268031</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>303702.514362609</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>319564.787653147</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>359874.205098995</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>371307.476034185</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>399093.820360421</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>420166.849217451</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>434307.308926959</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1859,144 +1864,144 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5.646</t>
+          <t>5646119.98507061</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.409</t>
+          <t>4408787.99999973</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4.326</t>
+          <t>4325718.00000254</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4.479</t>
+          <t>4479332.99999889</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4.265</t>
+          <t>4264815.99999884</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.204</t>
+          <t>4204459.99999896</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.155</t>
+          <t>4154912.00000056</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4.061</t>
+          <t>4061141.00000073</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4119574.00000038</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3970190.99999844</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>4.053</t>
+          <t>4052880.00000078</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4180301.00000205</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>4.234</t>
+          <t>4234087.99999993</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4329803.99999886</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>4.445</t>
+          <t>4444991.99999991</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>4.336</t>
+          <t>4336117.99999931</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>4.251</t>
+          <t>4251402.00000062</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>4.107</t>
+          <t>4106820.00000054</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>4.255</t>
+          <t>4255350.99999983</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>3.986</t>
+          <t>3986376.9219898</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>3.851</t>
+          <t>3850840.24965176</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>4.074</t>
+          <t>4073503.34664645</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>4.155</t>
+          <t>4154702.46463041</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4.424</t>
+          <t>4423576.37261882</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>4.778</t>
+          <t>4777741.79699768</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>5.066</t>
+          <t>5066180.92210099</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>5.142</t>
+          <t>5142137.11445436</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2006,144 +2011,144 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>45.393</t>
+          <t>45393286.9025001</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>34.161</t>
+          <t>34161000.0000034</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>34.115</t>
+          <t>34114999.9999985</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>34.036</t>
+          <t>34035999.9999999</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>34.447</t>
+          <t>34446999.999991</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>35.046</t>
+          <t>35045999.9999851</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>35.922</t>
+          <t>35921999.9999918</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>35.797</t>
+          <t>35797000.0000149</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>35.57</t>
+          <t>35569999.9999954</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>35.078</t>
+          <t>35078000.0000105</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>34.701</t>
+          <t>34701000.0000104</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>34.916</t>
+          <t>34915999.9999939</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>35.152</t>
+          <t>35151999.9999944</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>35.798</t>
+          <t>35798000.0000018</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>36.353</t>
+          <t>36352999.9999846</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>36.407</t>
+          <t>36407000.0000087</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>36.533</t>
+          <t>36532999.999996</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>37.024</t>
+          <t>37024000.0000007</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>37.489</t>
+          <t>37489000.0000014</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>38.166</t>
+          <t>38166131.885108</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>39.727</t>
+          <t>39726607.0748598</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>39439697.4837352</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>40.034</t>
+          <t>40034069.3714614</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>42.763</t>
+          <t>42762730.4783276</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>41.733</t>
+          <t>41732612.3343668</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>42.439</t>
+          <t>42439291.8832972</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>44.347</t>
+          <t>44346741.5734814</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2153,144 +2158,144 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.388</t>
+          <t>2387677.87731387</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.456</t>
+          <t>2455800.00000022</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2.484</t>
+          <t>2484399.99999993</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2.327</t>
+          <t>2327199.99999923</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.084</t>
+          <t>2084200.00000013</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.553</t>
+          <t>2553000.00000017</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.558</t>
+          <t>2557599.99999953</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.578</t>
+          <t>2577800.00000024</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2.593</t>
+          <t>2593300.00000053</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2.552</t>
+          <t>2552099.99999902</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2.603</t>
+          <t>2602899.9999999</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2.441</t>
+          <t>2441300.00000086</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2.653</t>
+          <t>2652900.00000017</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2.651</t>
+          <t>2650800.00000002</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2.597</t>
+          <t>2596500.00000047</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2.475</t>
+          <t>2474800.00000063</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2.457</t>
+          <t>2456500.0000001</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2.453</t>
+          <t>2452900.00000075</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2.438</t>
+          <t>2438100.00000024</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2.483</t>
+          <t>2483168.28689519</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2.617</t>
+          <t>2616677.68564623</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2.523</t>
+          <t>2523350.58801448</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2.513</t>
+          <t>2513272.51406862</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.509</t>
+          <t>2509464.07916989</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2.331</t>
+          <t>2330501.80922431</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2.283</t>
+          <t>2282844.24860043</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2.311</t>
+          <t>2311407.63813673</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2300,144 +2305,144 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16.011</t>
+          <t>16011074.780429</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>9.586</t>
+          <t>9585699.99999884</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>9.863</t>
+          <t>9863099.99999967</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>10.374</t>
+          <t>10374400.0000016</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>10.925</t>
+          <t>10924599.9999997</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>11.775</t>
+          <t>11775300.0000043</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12.652</t>
+          <t>12652099.9999988</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>13.202</t>
+          <t>13201900.0000045</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>13.931</t>
+          <t>13931400.0000007</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>14.615</t>
+          <t>14615100.0000038</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>15.134</t>
+          <t>15133999.9999965</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>16.122</t>
+          <t>16121800.0000015</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>16.809</t>
+          <t>16809400.0000013</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>17.394</t>
+          <t>17393999.999996</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>16.861</t>
+          <t>16860999.9999965</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>15.881</t>
+          <t>15880799.9999977</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>15.592</t>
+          <t>15591900.000001</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>15.394</t>
+          <t>15393899.9999969</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>14.574</t>
+          <t>14573500.0000002</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>14.065</t>
+          <t>14064544.2371013</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>13989775.6807254</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>14.662</t>
+          <t>14661963.8653006</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>14.886</t>
+          <t>14885572.6638664</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15.046</t>
+          <t>15045884.400281</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>15.451</t>
+          <t>15451199.0888343</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15.447</t>
+          <t>15447133.4689241</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>15.789</t>
+          <t>15789046.6848466</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2447,144 +2452,144 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.222</t>
+          <t>1221907.7643351</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.594</t>
+          <t>593599.999999948</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>564299.999999998</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.558</t>
+          <t>558200.000000003</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>558599.99999993</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.506</t>
+          <t>505600.000000006</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>544699.999999895</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.542</t>
+          <t>541800.000000065</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>552299.999999985</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.553</t>
+          <t>552500.000000113</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>551400.000000061</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.572</t>
+          <t>571799.999999999</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>604499.999999976</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>603099.999999966</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>602800.00000001</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.543</t>
+          <t>543200.000000033</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.519</t>
+          <t>519400.000000058</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>549800.000000159</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>559800.000000124</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.582</t>
+          <t>581789.115962037</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>560616.919581946</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>579545.928345649</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>614709.421884642</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>629546.282371839</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>694215.135029185</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.751</t>
+          <t>750718.521806677</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>0.767</t>
+          <t>766518.227497</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2594,144 +2599,144 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.009</t>
+          <t>2009267.29672399</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.772</t>
+          <t>1771700.00000013</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1774799.99999964</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.868</t>
+          <t>1867799.99999998</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1952500</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.092</t>
+          <t>2091900.00000005</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2129600.00000064</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.179</t>
+          <t>2179099.99999963</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2179699.99999967</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2.172</t>
+          <t>2172499.99999978</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2.163</t>
+          <t>2163299.99999971</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2.178</t>
+          <t>2177500.00000024</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2.211</t>
+          <t>2210600.0000006</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.258</t>
+          <t>2257700.00000038</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2.034</t>
+          <t>2033600.00000087</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2.114</t>
+          <t>2113500.00000064</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2.108</t>
+          <t>2107699.99999932</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2.133</t>
+          <t>2132700.00000041</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2.135</t>
+          <t>2135100.00000021</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2.062</t>
+          <t>2061533.51421916</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2.077</t>
+          <t>2077109.54492024</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2.083</t>
+          <t>2082778.27859179</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2089971.72500842</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.086</t>
+          <t>2086139.4178596</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2.196</t>
+          <t>2196386.40922068</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2089789.78842855</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2.109</t>
+          <t>2108881.06716577</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2741,144 +2746,144 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>21.496</t>
+          <t>21495921.0099892</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>18.739</t>
+          <t>18738999.9999988</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>21.366</t>
+          <t>21365999.9999931</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>21.611</t>
+          <t>21610999.999998</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>17.514</t>
+          <t>17514000.0000063</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>22.695</t>
+          <t>22694999.9999992</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>23.347</t>
+          <t>23347000.0000007</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>23.749</t>
+          <t>23749000.0000006</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>23879999.9999989</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>23.884</t>
+          <t>23884000.000012</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>23.888</t>
+          <t>23887999.9999958</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>24.034</t>
+          <t>24034000.0000023</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>24.299</t>
+          <t>24298999.9999922</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24649999.9999923</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>24.756</t>
+          <t>24755999.9999992</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>24.437</t>
+          <t>24437000.0000001</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>24.405</t>
+          <t>24405000.0000037</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>24.517</t>
+          <t>24517000.0000027</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>24.512</t>
+          <t>24512000.0000039</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>23.437</t>
+          <t>23436903.9980633</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>23.518</t>
+          <t>23517926.6569486</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>23.425</t>
+          <t>23425245.2885747</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>22.982</t>
+          <t>22981851.3396918</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>21.967</t>
+          <t>21967134.3741657</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>22.597</t>
+          <t>22596710.906806</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>22.529</t>
+          <t>22528920.9921925</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>22.255</t>
+          <t>22254540.0485394</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2888,144 +2893,144 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>29.418</t>
+          <t>29417835.6405701</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>22.885</t>
+          <t>22884699.9999999</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>23680199.9999991</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>24.152</t>
+          <t>24151700.0000004</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>24.591</t>
+          <t>24591100.0000034</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24420299.9999998</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>24.908</t>
+          <t>24908000.0000036</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>24.048</t>
+          <t>24048299.999991</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>25.357</t>
+          <t>25357099.999995</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>25.461</t>
+          <t>25461000.0000057</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>25.565</t>
+          <t>25564800.0000056</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>25.966</t>
+          <t>25966000.0000094</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>26.108</t>
+          <t>26108300.0000041</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>26.233</t>
+          <t>26233499.9999966</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>25.332</t>
+          <t>25331999.9999982</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>24.777</t>
+          <t>24777199.9999979</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>24.659</t>
+          <t>24659399.9999941</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>24709599.9999976</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>24.823</t>
+          <t>24823299.999991</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>24.619</t>
+          <t>24618743.6547123</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>26.749</t>
+          <t>26749352.8854372</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>30.816</t>
+          <t>30815604.1371804</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>27.325</t>
+          <t>27324875.1234989</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>26.391</t>
+          <t>26390976.2795109</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>27.638</t>
+          <t>27637877.1100358</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>28800082.3188842</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>29.006</t>
+          <t>29005829.1903475</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3035,144 +3040,144 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.056</t>
+          <t>2056042.77423784</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.129</t>
+          <t>2128500.00000079</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2169899.99999976</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2180499.99999934</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.332</t>
+          <t>2331999.99999881</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.408</t>
+          <t>2408499.99999965</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.446</t>
+          <t>2445600.00000135</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2.533</t>
+          <t>2533300.00000147</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2.607</t>
+          <t>2607199.99999953</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2.686</t>
+          <t>2686300.00000035</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2.817</t>
+          <t>2816900.00000156</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2.848</t>
+          <t>2848399.99999882</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2.903</t>
+          <t>2902699.99999947</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2.971</t>
+          <t>2971000.00000121</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2.993</t>
+          <t>2992500.00000006</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2.932</t>
+          <t>2931600.00000115</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2.825</t>
+          <t>2824999.99999893</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2.584</t>
+          <t>2583899.99999964</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2.339</t>
+          <t>2339499.99999972</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2.204</t>
+          <t>2204452.59065661</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2.028</t>
+          <t>2028485.74405725</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1989891.30662037</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>1.881</t>
+          <t>1881103.73358551</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.938</t>
+          <t>1938354.80878384</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.931</t>
+          <t>1930902.61267431</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>1.953</t>
+          <t>1952717.10825886</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1951534.40105872</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3182,144 +3187,144 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>4.061</t>
+          <t>4061169.02785563</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3.141</t>
+          <t>3141299.99999929</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3.047</t>
+          <t>3047300.00000037</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>3.025</t>
+          <t>3024600.00000103</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3.132</t>
+          <t>3132200.00000095</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.251</t>
+          <t>3251300.00000026</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.238</t>
+          <t>3238199.99999979</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3.387</t>
+          <t>3386799.99999914</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>3.266</t>
+          <t>3266400.00000029</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>3.493</t>
+          <t>3493300.00000059</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>3.418</t>
+          <t>3418099.99999886</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>3.383</t>
+          <t>3383100</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>3.523</t>
+          <t>3523499.99999971</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3.529</t>
+          <t>3528900.00000032</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>3.338</t>
+          <t>3338300.00000145</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3309700.00000008</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>3.316</t>
+          <t>3316499.99999891</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>3.351</t>
+          <t>3350599.9999989</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>3.423</t>
+          <t>3422599.99999997</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>3.352</t>
+          <t>3352110.57405659</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>3.349</t>
+          <t>3348624.51798807</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3540369.38224155</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>3.504</t>
+          <t>3504038.64768566</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>3.778</t>
+          <t>3777731.83950487</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>4.042</t>
+          <t>4041893.1056327</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>4.185</t>
+          <t>4184517.1088827</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>4.275</t>
+          <t>4274858.54150224</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3329,144 +3334,144 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>84.527</t>
+          <t>84526818.0711355</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>27.988</t>
+          <t>27988000.0000913</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>27.941</t>
+          <t>27941000.0001461</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>28.24</t>
+          <t>28239999.9998376</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>28.166</t>
+          <t>28166000.0002002</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>28.112</t>
+          <t>28111999.9999879</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>27.958</t>
+          <t>27958000.0000959</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27790000.0000611</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>27.206</t>
+          <t>27205999.999878</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26999999.9999987</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>26.444</t>
+          <t>26443999.9997725</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>26.458</t>
+          <t>26458499.9998362</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>28.528</t>
+          <t>28527899.9998918</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>28.575</t>
+          <t>28574999.9999002</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>28.599</t>
+          <t>28599299.9999709</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>28.652</t>
+          <t>28651900.0000897</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>28.633</t>
+          <t>28632699.999896</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>28.854</t>
+          <t>28854499.9999675</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>29.009</t>
+          <t>29009200.0001266</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>31.322</t>
+          <t>31322150.8385204</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>35.903</t>
+          <t>35902575.6719552</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>49.322</t>
+          <t>49322068.477336</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>51.98</t>
+          <t>51980395.9765228</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>58.088</t>
+          <t>58088369.5034487</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>59.385</t>
+          <t>59384958.8297588</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>64.621</t>
+          <t>64621138.2574661</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>68.271</t>
+          <t>68271308.475669</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3476,144 +3481,144 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>71.506</t>
+          <t>71506040.8998303</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>31.866</t>
+          <t>31865800.0000167</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>33.174</t>
+          <t>33173700.0000093</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>34.527</t>
+          <t>34526999.9999903</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>33.343</t>
+          <t>33342999.9999874</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>34.089</t>
+          <t>34088599.9999662</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>31.281</t>
+          <t>31281099.9999747</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>33.667</t>
+          <t>33666500.0000277</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>32.68</t>
+          <t>32679699.999994</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>32.707</t>
+          <t>32706900.000007</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>35.326</t>
+          <t>35326499.9999968</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>34.961</t>
+          <t>34961199.9999884</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>36.656</t>
+          <t>36656300.0000244</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>35.429</t>
+          <t>35428700.0000104</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>39.922</t>
+          <t>39921999.999921</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>41.051</t>
+          <t>41050600.0000193</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>43.109</t>
+          <t>43109499.9999721</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>40.647</t>
+          <t>40647499.9999953</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>47.082</t>
+          <t>47081899.9999954</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>44.266</t>
+          <t>44266440.102038</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>42.684</t>
+          <t>42684362.7990941</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>49.866</t>
+          <t>49865641.3007077</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>52.814</t>
+          <t>52814337.2734153</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>52.404</t>
+          <t>52403530.553433</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>51.112</t>
+          <t>51112296.0590308</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>57.265</t>
+          <t>57265212.3228809</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>60.435</t>
+          <t>60435094.7544518</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3623,144 +3628,144 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2.886</t>
+          <t>2885519.0002544</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.921</t>
+          <t>920899.999999925</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.017</t>
+          <t>1017199.99999993</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.081</t>
+          <t>1080799.99999997</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1130199.99999985</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.273</t>
+          <t>1272799.99999992</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1339800.00000031</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.399</t>
+          <t>1398699.99999946</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.407</t>
+          <t>1407199.99999997</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1468700.00000012</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1.496</t>
+          <t>1496200.00000027</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1.601</t>
+          <t>1600500.00000018</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>1.691</t>
+          <t>1691000.00000013</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>1.739</t>
+          <t>1738699.99999948</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1.727</t>
+          <t>1727100</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1537600.00000056</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1555199.99999952</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1539900.00000013</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1461500.00000004</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>1565241.46412062</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1618958.04495845</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2.077</t>
+          <t>2077046.40651549</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2.309</t>
+          <t>2309450.90419717</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2300386.84391838</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2.426</t>
+          <t>2426081.07584189</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2.607</t>
+          <t>2607227.07767039</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2.776</t>
+          <t>2776439.86816774</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3770,144 +3775,144 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>18.654</t>
+          <t>18653763.1138731</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>14660300.000001</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>14750300.0000003</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>14.87</t>
+          <t>14869599.9999968</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>15009500.0000009</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>15.255</t>
+          <t>15254999.9999965</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>15.505</t>
+          <t>15504600.0000012</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>15.872</t>
+          <t>15872400.0000087</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>16.265</t>
+          <t>16265199.9999964</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>16.512</t>
+          <t>16511599.9999961</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>16.605</t>
+          <t>16604900.000005</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>17.026</t>
+          <t>17026199.9999995</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>17.403</t>
+          <t>17403499.9999922</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>17.626</t>
+          <t>17626200.0000013</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>17.412</t>
+          <t>17411600.0000046</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>17.254</t>
+          <t>17253999.9999982</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>17.097</t>
+          <t>17097099.9999994</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>17.225</t>
+          <t>17225300.0000013</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>17.201</t>
+          <t>17201300.0000072</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>16.717</t>
+          <t>16716568.3797774</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>16.841</t>
+          <t>16840985.3880799</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17050165.7735219</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>17.177</t>
+          <t>17177475.2305278</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17.398</t>
+          <t>17397748.2390644</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>18.274</t>
+          <t>18273534.46103</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17.825</t>
+          <t>17824788.5729314</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>18.297</t>
+          <t>18296971.6907571</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3917,144 +3922,144 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>42.509</t>
+          <t>42508771.0995946</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>55.014</t>
+          <t>55014300.0000055</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>55.576</t>
+          <t>55575600.0000055</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>56.214</t>
+          <t>56213699.9999931</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>55.968</t>
+          <t>55968499.9999965</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55600100.000012</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>55.836</t>
+          <t>55836399.9999971</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>55.913</t>
+          <t>55912899.999993</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>55.379</t>
+          <t>55378600.0000008</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>55.368</t>
+          <t>55368299.9999916</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>55.511</t>
+          <t>55511499.9999894</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>55799500.0000139</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>56.733</t>
+          <t>56732699.9999841</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>57.145</t>
+          <t>57145300.0000004</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>57.137</t>
+          <t>57137200.0000031</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>54.88</t>
+          <t>54880000.000003</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>54.93</t>
+          <t>54930000.0000122</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>54.89</t>
+          <t>54890000.0000065</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>54620000.0000041</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>42.477</t>
+          <t>42476835.396543</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>42.542</t>
+          <t>42542478.7245932</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>43.861</t>
+          <t>43860662.7074203</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>46.66</t>
+          <t>46660235.4123072</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>43.486</t>
+          <t>43486076.6919876</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>42.956</t>
+          <t>42955996.5245537</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>45.652</t>
+          <t>45652049.0297952</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>45.244</t>
+          <t>45243523.440445</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4064,144 +4069,144 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>27.465</t>
+          <t>27464935.1663897</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>12.813</t>
+          <t>12812699.9999981</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>13.099</t>
+          <t>13098999.9999991</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>13.266</t>
+          <t>13266099.9999943</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>12.211</t>
+          <t>12210500.0000008</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>12.547</t>
+          <t>12547399.9999959</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>13.382</t>
+          <t>13382499.9999961</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>13.682</t>
+          <t>13681500.0000061</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>14.199</t>
+          <t>14199499.9999999</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>14.431</t>
+          <t>14430900.0000062</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>14.917</t>
+          <t>14916500.0000039</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>15.207</t>
+          <t>15207400.0000011</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>15.581</t>
+          <t>15581200.0000019</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>16.015</t>
+          <t>16014500.0000008</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>16.247</t>
+          <t>16247399.9999991</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>16.441</t>
+          <t>16441099.9999937</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>16.957</t>
+          <t>16957199.9999995</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>17.384</t>
+          <t>17384199.9999991</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>17.703</t>
+          <t>17702599.9999929</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>16.978</t>
+          <t>16978401.2111283</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>20640477.3032317</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>24.037</t>
+          <t>24036827.6346597</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>24.112</t>
+          <t>24111851.9507518</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>24.771</t>
+          <t>24771397.559498</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>24.899</t>
+          <t>24898785.5065045</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>24.866</t>
+          <t>24865880.3749196</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>24.905</t>
+          <t>24905112.6640106</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4211,144 +4216,144 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.754</t>
+          <t>1754473.02749608</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.226</t>
+          <t>1226200.00000018</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.216</t>
+          <t>1216400.00000002</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.238</t>
+          <t>1238399.99999975</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.245</t>
+          <t>1245000.00000008</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.231</t>
+          <t>1230900.00000018</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.187</t>
+          <t>1187099.99999994</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.124</t>
+          <t>1123900.00000015</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.145</t>
+          <t>1145200.00000001</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1.181</t>
+          <t>1180699.99999994</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1.175</t>
+          <t>1175299.99999995</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1.228</t>
+          <t>1227799.99999976</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1.225</t>
+          <t>1224699.99999972</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1.281</t>
+          <t>1280800.00000032</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1.258</t>
+          <t>1258399.99999978</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1159800.00000012</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1.112</t>
+          <t>1111899.99999983</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1.119</t>
+          <t>1119000.00000046</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>1.134</t>
+          <t>1134399.99999975</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1.153</t>
+          <t>1153106.8363299</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>1.185</t>
+          <t>1184666.45171633</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>1.214</t>
+          <t>1213565.88759357</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>1.251</t>
+          <t>1250631.87302865</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>1.348</t>
+          <t>1348380.98940016</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>1.493</t>
+          <t>1492581.55182544</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1529600.81364024</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1600490.69649031</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4358,144 +4363,144 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>300772.257343065</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>140900.000000024</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>146399.999999965</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>149299.999999943</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>146600.000000004</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>153600.000000026</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>157100.000000066</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>168800.000000009</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>167800.000000069</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>166800.000000051</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>165699.999999953</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>170999.999999952</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>177099.999999985</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>180500.000000024</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>178500.000000051</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>180999.999999983</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>180999.999999991</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>186400.000000002</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>195899.999999996</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>204805.342039276</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>233295.699057251</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>247784.517937457</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>256949.079818848</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>256540.909451853</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>263084.724811131</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>277633.769173426</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>285439.619335998</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4505,144 +4510,144 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.186</t>
+          <t>1185773.25689473</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.876</t>
+          <t>876499.999999758</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.842</t>
+          <t>841799.999999682</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.841</t>
+          <t>841000.000000356</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.793</t>
+          <t>793499.999999864</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.849</t>
+          <t>849400.000000323</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>843500.000000016</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.858</t>
+          <t>858399.999999827</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>897900.000000066</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>912599.999999746</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.933</t>
+          <t>933400.000000039</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.961</t>
+          <t>960800.000000336</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1.012</t>
+          <t>1012400.00000021</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.961</t>
+          <t>961400.000000025</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.953</t>
+          <t>953099.999999949</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>809800.000000105</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>760400.000000027</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0.713</t>
+          <t>712500.00000015</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0.763</t>
+          <t>763499.999999879</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>0.826</t>
+          <t>825928.76051265</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>786933.158179544</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>0.874</t>
+          <t>874342.650957085</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>0.826</t>
+          <t>826045.328155102</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>0.938</t>
+          <t>937774.68873516</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>0.994</t>
+          <t>994125.145982931</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>0.996</t>
+          <t>995551.87978817</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>1.022</t>
+          <t>1021804.88277301</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4652,144 +4657,144 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>50.717</t>
+          <t>50717110.9039033</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>18.311</t>
+          <t>18311499.9999925</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20.096</t>
+          <t>20095899.9999893</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>20.983</t>
+          <t>20983199.9999923</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22390000.0000014</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>22.865</t>
+          <t>22865000.0000174</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>24.157</t>
+          <t>24157000.0000099</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>24.022</t>
+          <t>24022099.9999873</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>24.389</t>
+          <t>24388899.9999921</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>24.662</t>
+          <t>24661900.0000136</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>25.517</t>
+          <t>25517099.9999933</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>26.009</t>
+          <t>26009399.9999992</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>27.307</t>
+          <t>27306800.0000078</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>27.833</t>
+          <t>27832900.0000104</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>28.612</t>
+          <t>28611800.000005</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>32469899.9999945</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>36.355</t>
+          <t>36354799.9999988</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>30.839</t>
+          <t>30838899.9999905</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>32.174</t>
+          <t>32173799.999994</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>33.853</t>
+          <t>33853156.7217459</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>39.18</t>
+          <t>39179877.8502566</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>37.425</t>
+          <t>37424828.1900382</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>32.214</t>
+          <t>32213855.5031311</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>37.858</t>
+          <t>37857824.7042282</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>39.253</t>
+          <t>39253282.9819557</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>43.017</t>
+          <t>43017155.3530884</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>44.294</t>
+          <t>44294497.9129124</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4799,144 +4804,144 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>289097.8000243</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>113460.000000023</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>124580.000000011</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>127899.999999993</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>129680.000000006</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>131430.000000029</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>132599.999999986</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>137400.000000021</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>134399.999999995</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>135899.999999957</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>132199.999999993</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>135100</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>131499.999999993</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>139899.999999982</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>136500.000000002</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>137099.999999991</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>138899.999999996</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>143899.999999986</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>147099.999999983</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>161057.863778182</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>183535.136929858</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>194260.929465188</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>208942.267834392</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>232736.03248834</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>261672.064450561</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>273424.893803899</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>280677.485027124</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4946,144 +4951,144 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>7.378</t>
+          <t>7378089.1493659</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>6.015</t>
+          <t>6014599.99999988</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6.001</t>
+          <t>6001399.99999819</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>6.203</t>
+          <t>6203300.00000089</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>6539900.00000046</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6679799.99999935</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>6.829</t>
+          <t>6829199.99999975</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>7039800.00000154</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>6.842</t>
+          <t>6842100.00000202</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>7.272</t>
+          <t>7271999.99999976</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>7.121</t>
+          <t>7120899.99999992</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>7.102</t>
+          <t>7101700.00000224</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>7.235</t>
+          <t>7235200.00000033</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>7.365</t>
+          <t>7364600.00000236</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>7.081</t>
+          <t>7080599.99999504</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>6.904</t>
+          <t>6903999.99999946</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>6.517</t>
+          <t>6517499.99999863</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>6.453</t>
+          <t>6452899.99999892</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>6.505</t>
+          <t>6505200.00000144</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>6.264</t>
+          <t>6263648.05848262</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>6.293</t>
+          <t>6292512.15792387</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>6.137</t>
+          <t>6136595.08315038</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>6.105</t>
+          <t>6105026.16304272</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>6.331</t>
+          <t>6331102.63926075</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>6.356</t>
+          <t>6356019.18012867</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>6.381</t>
+          <t>6381004.27121009</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>6.392</t>
+          <t>6392380.95515182</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5093,144 +5098,144 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>15.603</t>
+          <t>15603293.2711678</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10.762</t>
+          <t>10761800.0000002</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>10.936</t>
+          <t>10936199.9999994</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>10.931</t>
+          <t>10930799.9999997</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>10.927</t>
+          <t>10926500.0000044</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>10.735</t>
+          <t>10734700.0000007</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10.919</t>
+          <t>10918999.9999983</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>10.653</t>
+          <t>10652900.0000013</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>10.278</t>
+          <t>10277999.9999999</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>10.315</t>
+          <t>10315199.9999999</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>10.386</t>
+          <t>10385799.9999972</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>10.817</t>
+          <t>10816999.9999996</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>11.375</t>
+          <t>11375299.9999958</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>12.015</t>
+          <t>12014699.9999971</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>12.171</t>
+          <t>12170700.0000055</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>12.251</t>
+          <t>12251399.9999975</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>11.906</t>
+          <t>11906399.9999964</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>11.998</t>
+          <t>11998000.0000048</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>12.091</t>
+          <t>12091300.0000009</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>11.852</t>
+          <t>11851902.9580446</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>11.974</t>
+          <t>11974173.2897403</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>12.488</t>
+          <t>12488240.8933075</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>11.966</t>
+          <t>11965770.9833375</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12.888</t>
+          <t>12888285.9806944</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>13.189</t>
+          <t>13189378.4572808</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13999960.7366838</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>14.515</t>
+          <t>14514986.5800223</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5240,144 +5245,144 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>4.053</t>
+          <t>4053051.41472485</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3.233</t>
+          <t>3233200.00000022</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3.211</t>
+          <t>3211000.00000134</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>3.281</t>
+          <t>3280599.99999973</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3.488</t>
+          <t>3488400.0000005</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.583</t>
+          <t>3582599.99999917</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3.676</t>
+          <t>3676399.9999988</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>3.725</t>
+          <t>3724999.99999973</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>3.791</t>
+          <t>3791000.00000033</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3750000.0000002</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>3.786</t>
+          <t>3785500.00000016</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>3.781</t>
+          <t>3781499.99999921</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>3.864</t>
+          <t>3864399.99999873</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>3.871</t>
+          <t>3871499.99999972</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3869799.99999939</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>3.772</t>
+          <t>3771899.99999883</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>3.762</t>
+          <t>3761699.99999907</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>3.717</t>
+          <t>3717099.99999954</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>3.541</t>
+          <t>3540600.0000012</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>3.516</t>
+          <t>3516204.33512998</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>3.506</t>
+          <t>3506411.02761743</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>3.554</t>
+          <t>3554128.67106635</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3609645.50960509</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>3.829</t>
+          <t>3828661.07602125</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>3.922</t>
+          <t>3921850.91819159</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>3990024.08482992</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>4.039</t>
+          <t>4038731.40263205</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5387,144 +5392,144 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>11.655</t>
+          <t>11655274.4357218</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>6.436</t>
+          <t>6435699.99999712</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6.193</t>
+          <t>6192899.99999975</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>6.388</t>
+          <t>6387500.00000312</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>6.471</t>
+          <t>6470599.99999972</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6.171</t>
+          <t>6170799.99999733</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5.883</t>
+          <t>5883199.99999651</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>5.495</t>
+          <t>5495000.00000455</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>5.509</t>
+          <t>5508599.99999964</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>5.281</t>
+          <t>5281200.0000012</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>6.045</t>
+          <t>6044999.99999998</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>5.623</t>
+          <t>5623400.00000068</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>6.127</t>
+          <t>6126600.00000005</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6179599.99999889</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>6.172</t>
+          <t>6171599.99999676</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>6.082</t>
+          <t>6081999.99999841</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>5.447</t>
+          <t>5447099.99999975</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>5.525</t>
+          <t>5524700.00000162</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>5.743</t>
+          <t>5743200.00000059</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>6.366</t>
+          <t>6366499.48347335</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6750083.17167046</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>7.621</t>
+          <t>7620774.01277184</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>8.021</t>
+          <t>8020509.9667877</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>9.458</t>
+          <t>9457885.63958941</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>10.285</t>
+          <t>10284663.0057424</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10.513</t>
+          <t>10512568.6581505</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>10.717</t>
+          <t>10717001.4649583</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5534,144 +5539,144 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>63.434</t>
+          <t>63434087.7263739</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>57.08</t>
+          <t>57080199.9999977</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>57.159</t>
+          <t>57159099.9999937</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>56.397</t>
+          <t>56397499.9999927</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>55.782</t>
+          <t>55781899.9999927</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>56.11</t>
+          <t>56110100.0000087</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>58.51</t>
+          <t>58510000.00002</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>59.847</t>
+          <t>59846999.9999986</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>61.476</t>
+          <t>61476100.0000002</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>61.516</t>
+          <t>61515999.9999995</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>57.391</t>
+          <t>57390999.999984</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>62.866</t>
+          <t>62865999.9999916</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>63.62</t>
+          <t>63619999.9999958</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>65.368</t>
+          <t>65367999.9999942</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>62.035</t>
+          <t>62035099.9999633</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>64.094</t>
+          <t>64093700.0000029</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>64.978</t>
+          <t>64977500.000009</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>59.316</t>
+          <t>59315899.9999952</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>66.571</t>
+          <t>66570500.0000148</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>68.351</t>
+          <t>68351181.782047</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>59.304</t>
+          <t>59304349.967319</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>47.705</t>
+          <t>47705457.0893165</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>45.094</t>
+          <t>45094332.401741</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>53.848</t>
+          <t>53847706.4762979</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>53.744</t>
+          <t>53744408.85612</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>57.63</t>
+          <t>57630381.7109396</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>58.712</t>
+          <t>58712002.7605441</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5681,144 +5686,144 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2.597</t>
+          <t>2597115.88809901</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2.095</t>
+          <t>2095400.00000031</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2.172</t>
+          <t>2171700.00000009</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2.165</t>
+          <t>2164599.99999959</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2.095</t>
+          <t>2095100</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2.044</t>
+          <t>2044499.99999962</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2.003</t>
+          <t>2003199.99999964</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>1.988</t>
+          <t>1987899.99999963</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2.008</t>
+          <t>2007700.0000005</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2.033</t>
+          <t>2033200.00000056</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1.956</t>
+          <t>1955699.9999994</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2.003</t>
+          <t>2002799.99999956</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2049899.99999984</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2.123</t>
+          <t>2123100.0000007</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2.051</t>
+          <t>2051299.99999962</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1.992</t>
+          <t>1992200.00000013</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1.946</t>
+          <t>1945500.00000014</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1.945</t>
+          <t>1944799.99999983</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1959800.00000008</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1934141.98444168</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>1.945</t>
+          <t>1945310.16327179</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2.036</t>
+          <t>2035506.24033864</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>1.976</t>
+          <t>1976227.89193731</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>2.137</t>
+          <t>2137115.96861152</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2.154</t>
+          <t>2154328.94368728</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2.225</t>
+          <t>2225216.49981282</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>2.351</t>
+          <t>2351040.78117298</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5828,144 +5833,144 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>913205.35818361</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>758799.999999973</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.751</t>
+          <t>750999.999999982</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.753</t>
+          <t>752700.000000082</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.751</t>
+          <t>750900.000000314</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>746400.000000104</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>775800.000000032</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>779800.000000092</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.795</t>
+          <t>794899.999999991</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.795</t>
+          <t>795100.000000044</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>816700.000000017</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>829900.000000008</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>830100.000000113</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>850700.00000012</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>851200.000000046</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>816899.999999904</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>0.796</t>
+          <t>795700.000000219</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>774500.000000136</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>769300.000000015</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>0.755</t>
+          <t>755347.568254849</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>738853.06707971</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>0.766</t>
+          <t>765748.083060304</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>757196.391815487</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>790182.563245238</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>823918.391262486</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>859646.403734855</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>0.908</t>
+          <t>907539.863673011</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5975,144 +5980,144 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3.537</t>
+          <t>3537306.77707062</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.685</t>
+          <t>3685299.99999977</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3.632</t>
+          <t>3631999.99999891</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>3.586</t>
+          <t>3585900.00000032</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>3.524</t>
+          <t>3523800.00000047</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3.722</t>
+          <t>3721699.99999998</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3.808</t>
+          <t>3808200.00000019</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4009600.00000054</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>4.017</t>
+          <t>4017099.99999926</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>4.035</t>
+          <t>4035300.00000069</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>3.992</t>
+          <t>3991800.0000003</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>3.993</t>
+          <t>3992599.99999924</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4080100.00000145</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>4.183</t>
+          <t>4183400.00000056</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>4.095</t>
+          <t>4095399.999999</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>4.005</t>
+          <t>4004800.00000076</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>4.016</t>
+          <t>4016000.00000024</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>4.125</t>
+          <t>4124599.99999998</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>4.147</t>
+          <t>4147199.99999906</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>4.143</t>
+          <t>4142906.04849409</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>3.924</t>
+          <t>3924004.41567433</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>3.946</t>
+          <t>3946198.81694653</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>3.799</t>
+          <t>3798620.36906162</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>3.776</t>
+          <t>3775865.76864951</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3749757.26923105</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>3.696</t>
+          <t>3696342.77688602</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>3.508</t>
+          <t>3507706.96427656</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6122,144 +6127,144 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>17.757</t>
+          <t>17756971.2797153</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.426</t>
+          <t>8426400.00000533</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>8.903</t>
+          <t>8903499.99999714</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>9.288</t>
+          <t>9288200.00000428</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>9520199.9999981</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>9.567</t>
+          <t>9567200.00000625</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10.568</t>
+          <t>10567599.9999911</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>10.237</t>
+          <t>10236900.0000072</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>10.712</t>
+          <t>10711899.9999993</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>10.795</t>
+          <t>10794599.9999973</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>11.158</t>
+          <t>11157599.9999981</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>12.222</t>
+          <t>12221799.9999961</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>12.117</t>
+          <t>12117300.0000034</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>12.634</t>
+          <t>12634199.9999944</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>13.22</t>
+          <t>13220499.9999965</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>12.763</t>
+          <t>12762900.0000001</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>13.755</t>
+          <t>13754800.0000016</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>14.867</t>
+          <t>14867100.0000011</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>15.614</t>
+          <t>15614200.0000025</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>15.658</t>
+          <t>15657684.6240119</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>15.118</t>
+          <t>15118101.2615038</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>16.367</t>
+          <t>16367168.328585</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>16.276</t>
+          <t>16276490.2888134</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15.613</t>
+          <t>15613234.7219459</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>13.786</t>
+          <t>13786012.5647161</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>13920080.0933508</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>14.636</t>
+          <t>14635914.2511294</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6269,144 +6274,144 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>10.195</t>
+          <t>10194944.7734318</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>6.198</t>
+          <t>6198100.0000009</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6.349</t>
+          <t>6349200.00000081</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>6.344</t>
+          <t>6344400.00000228</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>6.306</t>
+          <t>6305700.00000107</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6.095</t>
+          <t>6095099.99999936</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>6.357</t>
+          <t>6357399.99999744</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>6.096</t>
+          <t>6096100.00000147</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5919500.00000028</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>6.095</t>
+          <t>6094900.00000083</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>6.306</t>
+          <t>6306199.99999994</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>6.237</t>
+          <t>6236999.99999876</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>6.395</t>
+          <t>6395399.99999889</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>6.549</t>
+          <t>6548500.00000201</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>6.827</t>
+          <t>6827199.99999854</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>7.083</t>
+          <t>7082900.00000152</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>7.178</t>
+          <t>7178400.00000084</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>7.475</t>
+          <t>7475200.00000219</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>7.596</t>
+          <t>7595700.00000062</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>7.433</t>
+          <t>7433222.21556335</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>7.626</t>
+          <t>7626473.3239277</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>8.727</t>
+          <t>8726627.31660215</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>8.611</t>
+          <t>8610578.76947349</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>9.257</t>
+          <t>9256731.15401428</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>9.261</t>
+          <t>9261017.19191152</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>9.609</t>
+          <t>9608961.10519592</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>9.646</t>
+          <t>9646402.77753172</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6416,144 +6421,144 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>200.156</t>
+          <t>200155947.04188</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>114.86</t>
+          <t>114860399.999962</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>117.176</t>
+          <t>117175500.00001</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>107.186</t>
+          <t>107185900.000019</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>123.273</t>
+          <t>123273399.999981</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>126.217</t>
+          <t>126216800.000007</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>128.941</t>
+          <t>128941000.000032</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>129.087</t>
+          <t>129086999.999992</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>128.854</t>
+          <t>128853999.999979</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>114.314</t>
+          <t>114313999.999987</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>131.143</t>
+          <t>131143000.000007</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>117.489</t>
+          <t>117488999.999984</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>136.094</t>
+          <t>136094000.000022</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>137.871</t>
+          <t>137871000.000001</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>137.581</t>
+          <t>137581000.000036</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>132.355</t>
+          <t>132355000.000006</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>131.701</t>
+          <t>131701000.000035</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>114.339</t>
+          <t>114338999.999994</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>135.224</t>
+          <t>135223999.999992</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>132.544</t>
+          <t>132543718.741931</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>136.388</t>
+          <t>136387545.287464</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>173.1</t>
+          <t>173099970.839227</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>173.696</t>
+          <t>173695782.594263</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>179.721</t>
+          <t>179721247.914089</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>174.444</t>
+          <t>174443655.026558</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>196.205</t>
+          <t>196205069.240423</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>197.869</t>
+          <t>197869497.498466</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6565,7 +6570,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6575,144 +6580,144 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2397.238</t>
+          <t>2397237689.94836</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1010.923</t>
+          <t>1010922944.0441</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1199.235</t>
+          <t>1199235409.84141</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1210.63</t>
+          <t>1210630433.00015</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1198.223</t>
+          <t>1198223382.08405</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1249.011</t>
+          <t>1249011334.99981</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1262.331</t>
+          <t>1262331377.00031</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>1282.979</t>
+          <t>1282979381.0003</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1307.228</t>
+          <t>1307228483.99982</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1325.152</t>
+          <t>1325152161.00007</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1365.398</t>
+          <t>1365398164.99947</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>1380.875</t>
+          <t>1380874830.99982</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>1433.558</t>
+          <t>1433557617.99937</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>1491.668</t>
+          <t>1491668234.00004</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>1485.384</t>
+          <t>1485383547.00007</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1516.619</t>
+          <t>1516618618.00037</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1576.852</t>
+          <t>1576852067.00007</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1549.631</t>
+          <t>1549631194.99977</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>1594.722</t>
+          <t>1594721801.00009</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>1617.766</t>
+          <t>1617765845.78776</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>1623.331</t>
+          <t>1623330653.70467</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>1793.077</t>
+          <t>1793076630.9851</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>1768.501</t>
+          <t>1768500917.40007</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>1846.456</t>
+          <t>1846455785.00133</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>1870.706</t>
+          <t>1870705973.81567</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2023.138</t>
+          <t>2023138495.80353</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>2086.421</t>
+          <t>2086420813.30221</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6722,144 +6727,144 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>1421914.21455013</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.078</t>
+          <t>1077999.99999981</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1119600.00000002</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.172</t>
+          <t>1171999.99999966</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1219899.99999967</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1140499.99999993</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1.241</t>
+          <t>1241300.00000012</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>1165300.00000017</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1.193</t>
+          <t>1193399.9999996</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1.211</t>
+          <t>1211300.00000026</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1.256</t>
+          <t>1255799.99999988</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>1.237</t>
+          <t>1237499.99999971</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>1.268</t>
+          <t>1268499.99999999</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1324599.99999965</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>1.281</t>
+          <t>1281400.00000016</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1.258</t>
+          <t>1257800.00000028</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1.192</t>
+          <t>1192199.99999983</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1.153</t>
+          <t>1152799.99999977</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>1.137</t>
+          <t>1136900.00000027</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>1.149</t>
+          <t>1148805.70938101</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>1.154</t>
+          <t>1153944.40868979</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>1.141</t>
+          <t>1141130.43177415</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>1.209</t>
+          <t>1209415.63729113</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>1.185</t>
+          <t>1184960.50732434</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>1.289</t>
+          <t>1288793.98688244</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>1.307</t>
+          <t>1306644.16473266</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>1.372</t>
+          <t>1371642.23566283</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6869,144 +6874,144 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>3.609</t>
+          <t>3609213.69709116</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>3.059</t>
+          <t>3059299.99999927</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2.714</t>
+          <t>2714299.99999877</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>3.016</t>
+          <t>3016099.99999975</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>3.066</t>
+          <t>3066199.99999925</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2.743</t>
+          <t>2743200.00000028</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2.733</t>
+          <t>2732674.99999867</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2.895</t>
+          <t>2895049.99999947</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2.891</t>
+          <t>2890725.00000002</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>3.281</t>
+          <t>3280999.99999882</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2.911</t>
+          <t>2911199.99999927</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2.929</t>
+          <t>2928800.00000008</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2.982</t>
+          <t>2982000.00000068</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>3.456</t>
+          <t>3456299.9999995</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2.918</t>
+          <t>2917500.00000029</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>3.474</t>
+          <t>3473799.99999948</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>3.033</t>
+          <t>3033199.99999971</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>3.589</t>
+          <t>3588800.00000046</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>3.641</t>
+          <t>3640900.00000084</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>3.644</t>
+          <t>3644130.19286549</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>3.489</t>
+          <t>3489446.401301</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>3.842</t>
+          <t>3841927.42770372</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>3.821</t>
+          <t>3820585.57969366</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3.653</t>
+          <t>3652716.90618879</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>3.517</t>
+          <t>3517351.58405624</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>3.705</t>
+          <t>3705314.51833295</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>3.598</t>
+          <t>3598494.18045673</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7016,144 +7021,144 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2.162</t>
+          <t>2162267.88553028</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1934100.00000035</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2.014</t>
+          <t>2014399.99999994</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2.076</t>
+          <t>2076300.00000005</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2.139</t>
+          <t>2138600.0000003</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2.171</t>
+          <t>2170799.99999969</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2.191</t>
+          <t>2191299.99999935</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2.195</t>
+          <t>2194599.99999962</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2.202</t>
+          <t>2202499.99999979</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2.169</t>
+          <t>2168800.00000056</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2180199.99999998</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2190200.00000071</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2.235</t>
+          <t>2235300.00000055</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2.324</t>
+          <t>2323700.00000047</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2.257</t>
+          <t>2257000.00000021</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2.296</t>
+          <t>2295599.99999952</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>2.306</t>
+          <t>2306200.00000019</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2.355</t>
+          <t>2354500.00000034</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2.402</t>
+          <t>2401999.99999967</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2.383</t>
+          <t>2382885.90362619</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>2.255</t>
+          <t>2254903.11108702</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2.082</t>
+          <t>2081942.99141596</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>1.999</t>
+          <t>1998671.84578176</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>2.014</t>
+          <t>2014080.38260557</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>1.956</t>
+          <t>1956352.72405781</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>1.983</t>
+          <t>1983225.90281679</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>2.134</t>
+          <t>2133913.64311397</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7163,144 +7168,144 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>10.928</t>
+          <t>10927764.9675137</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>9.717</t>
+          <t>9716799.99999709</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>9.865</t>
+          <t>9864700.00000575</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>9.728</t>
+          <t>9728000.00000096</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>9.356</t>
+          <t>9355900.00000008</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>9.155</t>
+          <t>9155399.99999993</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>8.257</t>
+          <t>8257199.99999817</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>7.927</t>
+          <t>7927400.00000291</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>8.067</t>
+          <t>8067399.99999988</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>8.083</t>
+          <t>8082799.99999896</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>8.164</t>
+          <t>8163500.00000077</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>8.437</t>
+          <t>8437100.00000084</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>8.822</t>
+          <t>8821599.9999981</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>9.201</t>
+          <t>9200600.0000012</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>9.316</t>
+          <t>9315799.99999704</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>8.976</t>
+          <t>8976099.99999841</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>8.781</t>
+          <t>8781400.0000005</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>9.006</t>
+          <t>9005900.00000027</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>9.101</t>
+          <t>9101099.99999749</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>7.945</t>
+          <t>7944583.19824758</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>7.789</t>
+          <t>7788558.60375214</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>8.721</t>
+          <t>8720727.34576425</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>8.378</t>
+          <t>8378444.97152311</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8960012.79916397</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>9.272</t>
+          <t>9272455.85645717</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9299840.03242024</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>9.359</t>
+          <t>9359107.79250242</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7310,144 +7315,144 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>410.522</t>
+          <t>410521736.730245</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>67.591</t>
+          <t>67590936.044069</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>120.137</t>
+          <t>120136999.99995</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>123.042</t>
+          <t>123042000.000101</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>145.331</t>
+          <t>145330999.999955</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>145.489</t>
+          <t>145488999.999927</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>147.584</t>
+          <t>147584000.00018</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>155.386</t>
+          <t>155386000.000109</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>166.374</t>
+          <t>166373999.999902</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>183.359</t>
+          <t>183358999.999949</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>192.643</t>
+          <t>192642999.999953</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>200.094</t>
+          <t>200093999.999975</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>203.956</t>
+          <t>203955999.999946</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>224.072</t>
+          <t>224071999.999999</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>228.691</t>
+          <t>228691000.000072</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>238.196</t>
+          <t>238196000.000222</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>246.135</t>
+          <t>246135000.000078</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>231.226</t>
+          <t>231226000.00006</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>221.405</t>
+          <t>221405000.000093</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>219.192</t>
+          <t>219191715.888086</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>218.871</t>
+          <t>218871413.871164</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>243.879</t>
+          <t>243879396.761465</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>244.634</t>
+          <t>244634425.101417</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>257.521</t>
+          <t>257521068.580147</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>261.808</t>
+          <t>261807814.794267</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>289.832</t>
+          <t>289832069.899892</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>310.542</t>
+          <t>310542459.465846</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7457,144 +7462,144 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>74.509</t>
+          <t>74509447.3147788</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>24.265</t>
+          <t>24264999.999996</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>56.908</t>
+          <t>56907999.9999951</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>56.743</t>
+          <t>56742999.99998</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>57.741</t>
+          <t>57741000.0000133</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>59.425</t>
+          <t>59424999.9999887</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>60.347</t>
+          <t>60347000.0000219</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>61.307</t>
+          <t>61306999.9999832</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>63.056</t>
+          <t>63056000.0000018</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>65.244</t>
+          <t>65244000.0000042</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>65.172</t>
+          <t>65172000.0000104</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>67.011</t>
+          <t>67010999.9999847</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>68.675</t>
+          <t>68674999.9999685</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>73.609</t>
+          <t>73608999.9999862</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>75.095</t>
+          <t>75095000.0000155</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>84.189</t>
+          <t>84188999.9999789</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>96.846</t>
+          <t>96845999.9999956</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>83.478</t>
+          <t>83477999.9999924</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>82.989</t>
+          <t>82988999.9999959</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>81.001</t>
+          <t>81001443.9418646</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>78.245</t>
+          <t>78245389.5250459</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>89.136</t>
+          <t>89136356.6359679</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>79.044</t>
+          <t>79043790.2415006</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>81.068</t>
+          <t>81067673.1916988</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>72.241</t>
+          <t>72240501.4931422</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>70.18</t>
+          <t>70180454.2369931</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>69.276</t>
+          <t>69276413.5133622</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7604,144 +7609,144 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>163.358</t>
+          <t>163358441.707371</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>53.457</t>
+          <t>53457000.0000214</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>101.195</t>
+          <t>101195000.000018</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>103.744</t>
+          <t>103744000.000014</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>104.887</t>
+          <t>104886999.999991</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>106.722</t>
+          <t>106722000.000019</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>107.764</t>
+          <t>107764000.000003</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>110.058</t>
+          <t>110058000.000055</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>112.738</t>
+          <t>112738000.000036</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>115.426</t>
+          <t>115425999.999979</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>117.204</t>
+          <t>117203999.999981</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>118.622</t>
+          <t>118622000.000026</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>120.783</t>
+          <t>120783000.000041</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>124.526</t>
+          <t>124526000.000035</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>124.131</t>
+          <t>124130999.999991</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>126.008</t>
+          <t>126007999.999999</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>127.798</t>
+          <t>127797999.999973</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>130.975</t>
+          <t>130975000.000001</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>129.348</t>
+          <t>129348000.000008</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>131.528</t>
+          <t>131527778.652998</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>111.395</t>
+          <t>111394585.861601</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>102.937</t>
+          <t>102936805.19165</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>102.358</t>
+          <t>102357899.056346</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>113.834</t>
+          <t>113833601.186524</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>122.943</t>
+          <t>122942554.704332</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>137.437</t>
+          <t>137437300.704466</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>141.382</t>
+          <t>141382484.220816</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7751,144 +7756,144 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>421.049</t>
+          <t>421049004.851846</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>151.57</t>
+          <t>151570000.000031</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>193.136</t>
+          <t>193136461.841281</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>199.224</t>
+          <t>199224000.000068</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>178.221</t>
+          <t>178220631.084091</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>209.804</t>
+          <t>209803999.99993</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>215.542</t>
+          <t>215542000.00005</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>221.794</t>
+          <t>221794000.000003</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>228.11</t>
+          <t>228109999.999991</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>234.322</t>
+          <t>234321999.999969</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>240.183</t>
+          <t>240182999.99999</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>245.13</t>
+          <t>245129999.999942</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>251.235</t>
+          <t>251234999.999897</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>264.129</t>
+          <t>264129000.000067</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>268.167</t>
+          <t>268166999.999911</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>273.668</t>
+          <t>273667999.999991</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>282.859</t>
+          <t>282859000.000004</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>293.758</t>
+          <t>293757999.999862</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>304.271</t>
+          <t>304271000.000001</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>322.021</t>
+          <t>322021350.749113</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>326.709</t>
+          <t>326708748.308696</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>353.593</t>
+          <t>353592595.641752</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>338.213</t>
+          <t>338212974.756416</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>342.196</t>
+          <t>342195671.459443</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>343.657</t>
+          <t>343657055.006519</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>376.266</t>
+          <t>376265735.332635</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>385.211</t>
+          <t>385211404.766883</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7898,137 +7903,137 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>28.688</t>
+          <t>28688129.9306861</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>7840199.99998846</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>8.194</t>
+          <t>8194299.99999937</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>14.265</t>
+          <t>14264999.9999962</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>8.292</t>
+          <t>8292200.00000747</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>14.785</t>
+          <t>14784599.9999933</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>13.358</t>
+          <t>13358300.0000061</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>14829800.0000056</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>15.889</t>
+          <t>15889100.0000053</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>17.163</t>
+          <t>17163100.0000024</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>18.043</t>
+          <t>18043200.0000043</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>18.441</t>
+          <t>18441200.0000082</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>20.264</t>
+          <t>20263699.9999954</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>22.946</t>
+          <t>22945700.0000094</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>23.957</t>
+          <t>23956500.0000125</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>24559799.9999999</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>26.508</t>
+          <t>26507899.9999998</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>27.381</t>
+          <t>27380799.9999996</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>28.029</t>
+          <t>28029000.0000068</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>26.144</t>
+          <t>26144289.2801435</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>24.956</t>
+          <t>24956262.1704564</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26.485</t>
+          <t>26484695.2902657</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>25.907</t>
+          <t>25907276.4164936</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>25.784</t>
+          <t>25784251.9985426</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>25.931</t>
+          <t>25930789.4779931</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>27.467</t>
+          <t>27466607.5592235</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>28.541</t>
+          <t>28540592.8878475</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8067,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Number of employee</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -8104,6 +8114,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
